--- a/tests/fixtures/danone/ampliacion_servicios.xlsx
+++ b/tests/fixtures/danone/ampliacion_servicios.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MODELO-A100</t>
+          <t>CH170</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -641,11 +641,7 @@
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MODELO-A100</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>FAB-D-0012</t>
